--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.742283179790153</v>
+        <v>0.9331210167158999</v>
       </c>
       <c r="D2" t="n">
-        <v>4.018533695491151</v>
+        <v>0.653011725517312</v>
       </c>
       <c r="E2" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F2" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.22510341796167</v>
+        <v>7.674079305418772</v>
       </c>
       <c r="D3" t="n">
-        <v>44.63782201794293</v>
+        <v>7.253646077915726</v>
       </c>
       <c r="E3" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F3" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.02068854342302</v>
+        <v>4.878361888306242</v>
       </c>
       <c r="D4" t="n">
-        <v>30.15985887107495</v>
+        <v>4.90097706654968</v>
       </c>
       <c r="E4" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F4" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.83288640571854</v>
+        <v>3.385344040929262</v>
       </c>
       <c r="D5" t="n">
-        <v>21.129761082968</v>
+        <v>3.4335861759823</v>
       </c>
       <c r="E5" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F5" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.10857620726025</v>
+        <v>5.867643633679791</v>
       </c>
       <c r="D6" t="n">
-        <v>27.85373006885293</v>
+        <v>4.526231136188601</v>
       </c>
       <c r="E6" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F6" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.13692390855885</v>
+        <v>3.109750135140814</v>
       </c>
       <c r="D7" t="n">
-        <v>18.96337050927429</v>
+        <v>3.081547707757073</v>
       </c>
       <c r="E7" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F7" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.21436287272162</v>
+        <v>7.184833966817263</v>
       </c>
       <c r="D8" t="n">
-        <v>43.98229383341037</v>
+        <v>7.147122747929185</v>
       </c>
       <c r="E8" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F8" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.75607949266835</v>
+        <v>3.210362917558607</v>
       </c>
       <c r="D9" t="n">
-        <v>19.49367322989137</v>
+        <v>3.167721899857348</v>
       </c>
       <c r="E9" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F9" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.65661159306139</v>
+        <v>4.819199383872475</v>
       </c>
       <c r="D10" t="n">
-        <v>29.56875661044278</v>
+        <v>4.804922949196952</v>
       </c>
       <c r="E10" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F10" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.77171877772573</v>
+        <v>6.462904301380432</v>
       </c>
       <c r="D11" t="n">
-        <v>39.461152196128</v>
+        <v>6.4124372318708</v>
       </c>
       <c r="E11" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F11" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.96412172103863</v>
+        <v>5.519169779668777</v>
       </c>
       <c r="D12" t="n">
-        <v>33.85287082146025</v>
+        <v>5.501091508487291</v>
       </c>
       <c r="E12" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F12" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.10098144102903</v>
+        <v>5.216409484167217</v>
       </c>
       <c r="D13" t="n">
-        <v>31.81504564359019</v>
+        <v>5.169944917083407</v>
       </c>
       <c r="E13" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F13" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.33136406046239</v>
+        <v>5.578846659825139</v>
       </c>
       <c r="D14" t="n">
-        <v>34.22083330196148</v>
+        <v>5.560885411568742</v>
       </c>
       <c r="E14" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F14" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.21630584786358</v>
+        <v>7.022649700277832</v>
       </c>
       <c r="D15" t="n">
-        <v>43.05430927688948</v>
+        <v>6.996325257494541</v>
       </c>
       <c r="E15" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F15" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.444206838055</v>
+        <v>6.734683611183937</v>
       </c>
       <c r="D16" t="n">
-        <v>41.20016704846271</v>
+        <v>6.695027145375191</v>
       </c>
       <c r="E16" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F16" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>46.14324309811129</v>
+        <v>7.498277003443085</v>
       </c>
       <c r="D17" t="n">
-        <v>45.85175825948047</v>
+        <v>7.450910717165576</v>
       </c>
       <c r="E17" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F17" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>23.68377316035414</v>
+        <v>3.848613138557547</v>
       </c>
       <c r="D18" t="n">
-        <v>23.68506327249775</v>
+        <v>3.848822781780885</v>
       </c>
       <c r="E18" t="n">
-        <v>11.08804582340106</v>
+        <v>1.801807446302673</v>
       </c>
       <c r="F18" t="n">
-        <v>11.06664207278908</v>
+        <v>1.798329336828225</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
